--- a/output/2.7_各部门AI-IDE使用情况汇总.xlsx
+++ b/output/2.7_各部门AI-IDE使用情况汇总.xlsx
@@ -449,17 +449,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>渲染组</t>
+          <t>工具前端部</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>8</v>
+        <v>23</v>
       </c>
       <c r="D2" t="n">
-        <v>34</v>
+        <v>120</v>
       </c>
       <c r="E2" t="n">
-        <v>23.5</v>
+        <v>19.2</v>
       </c>
     </row>
     <row r="3">
@@ -487,17 +487,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>工具前端部</t>
+          <t>渲染组</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="D4" t="n">
-        <v>120</v>
+        <v>34</v>
       </c>
       <c r="E4" t="n">
-        <v>14.2</v>
+        <v>11.8</v>
       </c>
     </row>
     <row r="5">
@@ -510,13 +510,13 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="D5" t="n">
         <v>125</v>
       </c>
       <c r="E5" t="n">
-        <v>6.4</v>
+        <v>8.800000000000001</v>
       </c>
     </row>
     <row r="6">
@@ -525,17 +525,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Coohom技术与数据开发组</t>
+          <t>算力中心</t>
         </is>
       </c>
       <c r="C6" t="n">
         <v>2</v>
       </c>
       <c r="D6" t="n">
-        <v>59</v>
+        <v>27</v>
       </c>
       <c r="E6" t="n">
-        <v>3.4</v>
+        <v>7.4</v>
       </c>
     </row>
     <row r="7">
@@ -544,17 +544,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>KooLab组</t>
+          <t>Coohom技术与数据开发组</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D7" t="n">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="E7" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
     </row>
     <row r="8">
@@ -563,17 +563,17 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>算力中心</t>
+          <t>KooLab组</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>27</v>
+        <v>57</v>
       </c>
       <c r="E8" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
     </row>
     <row r="9">
